--- a/PM/SkienAlgsListPM2025.xlsx
+++ b/PM/SkienAlgsListPM2025.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urfume-my.sharepoint.com/personal/sergey_osipov_urfu_me/Documents/AiSD2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urfume-my.sharepoint.com/personal/sergey_osipov_urfu_me/Documents/AiSD2026/PM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1260" documentId="13_ncr:1_{BB64072A-02B6-4C3F-B1E2-71C6B558E3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7F160F6-5F4F-4C42-B64A-37E662D4122D}"/>
+  <xr:revisionPtr revIDLastSave="1297" documentId="13_ncr:1_{BB64072A-02B6-4C3F-B1E2-71C6B558E3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35BC7EB5-76C1-4E73-B4C1-35E98C180939}"/>
   <bookViews>
-    <workbookView xWindow="705" yWindow="420" windowWidth="27540" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="660" windowWidth="24660" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" refMode="R1C1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="323">
   <si>
     <t>Листинг</t>
   </si>
@@ -1009,13 +1009,34 @@
   </si>
   <si>
     <t>Дата доклада</t>
+  </si>
+  <si>
+    <t>Толстобров Дмитрий Александрович</t>
+  </si>
+  <si>
+    <t>Подобытько Владимир Дмитриевич</t>
+  </si>
+  <si>
+    <t>Путинцев Александр Алексеевич</t>
+  </si>
+  <si>
+    <t>Опойков Егор Владимирович</t>
+  </si>
+  <si>
+    <t>Корнешов Дмитрий Александрович</t>
+  </si>
+  <si>
+    <t>Тюхтин Георгий Алексеевич</t>
+  </si>
+  <si>
+    <t>Бельков Сергей Дмитриевич</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1079,14 +1100,6 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -1161,7 +1174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1185,74 +1198,50 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1274,6 +1263,7 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1402,7 +1392,6 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1446,13 +1435,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5609EA63-45AF-4126-A392-111B73C106A8}" name="Таблица1" displayName="Таблица1" ref="A1:G107" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:G107" xr:uid="{5609EA63-45AF-4126-A392-111B73C106A8}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{93552DC0-400C-4041-9CCE-C18FD2B6831E}" name="Листинг" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{9E9E2B49-CA37-44D6-8AE2-28CC5F771432}" name="Имя" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{9435CBF6-ED5E-4320-A96F-556C3F73813F}" name="Название" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{52068E18-F2F5-450F-8D7A-7092B4AF0E59}" name="Страница" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{4EEEFFB7-77F0-4CC9-8ED1-B24C16B04254}" name="Строк" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{93552DC0-400C-4041-9CCE-C18FD2B6831E}" name="Листинг" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{9E9E2B49-CA37-44D6-8AE2-28CC5F771432}" name="Имя" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{9435CBF6-ED5E-4320-A96F-556C3F73813F}" name="Название" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{52068E18-F2F5-450F-8D7A-7092B4AF0E59}" name="Страница" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{4EEEFFB7-77F0-4CC9-8ED1-B24C16B04254}" name="Строк" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{19F840D8-A240-40D0-A93F-75D2D6A18B2C}" name="Студент, отвечает за код" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{A7989D18-D756-4842-B2F4-DE249D9B736C}" name="Дата доклада" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{A7989D18-D756-4842-B2F4-DE249D9B736C}" name="Дата доклада" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1700,2257 +1689,2327 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="3">
         <v>26</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="3">
         <v>11</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="3" cm="1">
-        <f t="array" ref="H2">_xlfn.UNIQUE($F$2:$F$107)</f>
-        <v>0</v>
+      <c r="F2" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="H2" s="3" t="str" cm="1">
+        <f t="array" ref="H2:H9">_xlfn.UNIQUE($F$2:$F$107)</f>
+        <v>Толстобров Дмитрий Александрович</v>
       </c>
       <c r="I2" s="4">
         <f>SUMIF(F2:F107, H2, E2:E107)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3">
+        <v>67</v>
+      </c>
+      <c r="E3" s="3">
+        <v>13</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="H3" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="16">
-        <v>67</v>
-      </c>
-      <c r="E3" s="16">
-        <v>13</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="3"/>
       <c r="I3" s="4">
         <f>SUMIF(F3:F108, H3, E3:E108)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="3">
         <v>69</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="3">
         <v>16</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="3"/>
+      <c r="F4" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="3" t="str">
+        <v>Подобытько Владимир Дмитриевич</v>
+      </c>
       <c r="I4" s="4">
         <f>SUMIF(F4:F108, H4, E4:E108)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="3">
         <v>71</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="3">
         <v>8</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="3"/>
+      <c r="F5" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="3" t="str">
+        <v>Тюхтин Георгий Алексеевич</v>
+      </c>
       <c r="I5" s="4">
-        <f>SUMIF(F5:F108, H5, E5:E108)</f>
-        <v>0</v>
+        <f t="shared" ref="I5:I50" si="0">SUMIF(F5:F108, H5, E5:E108)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="3">
         <v>77</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="3">
         <v>5</v>
       </c>
       <c r="F6" s="11"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="3"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="3" t="str">
+        <v>Опойков Егор Владимирович</v>
+      </c>
       <c r="I6" s="4">
-        <f>SUMIF(F6:F109, H6, E6:E109)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="3">
         <v>99</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="3">
         <v>4</v>
       </c>
       <c r="F7" s="11"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="3"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="3" t="str">
+        <v>Путинцев Александр Алексеевич</v>
+      </c>
       <c r="I7" s="4">
-        <f>SUMIF(F7:F110, H7, E7:E110)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="3">
         <v>99</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="3">
         <v>10</v>
       </c>
       <c r="F8" s="11"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="3"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="3" t="str">
+        <v>Бельков Сергей Дмитриевич</v>
+      </c>
       <c r="I8" s="4">
-        <f>SUMIF(F8:F111, H8, E8:E111)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="3">
         <v>7</v>
       </c>
       <c r="F9" s="11"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="5"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="5" t="str">
+        <v>Корнешов Дмитрий Александрович</v>
+      </c>
       <c r="I9" s="4">
-        <f>SUMIF(F9:F112, H9, E9:E112)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="3">
         <v>10</v>
       </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="26"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="3"/>
       <c r="I10" s="4">
-        <f>SUMIF(F10:F113, H10, E10:E113)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="3">
         <v>101</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="3">
         <v>12</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="26"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4">
-        <f>SUMIF(F11:F114, H11, E11:E114)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="3">
         <v>110</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="3">
         <v>6</v>
       </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="24"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="14"/>
       <c r="H12" s="3"/>
       <c r="I12" s="4">
-        <f>SUMIF(F12:F115, H12, E12:E115)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="3">
         <v>110</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="3">
         <v>13</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="24"/>
+      <c r="F13" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="G13" s="14"/>
       <c r="H13" s="3"/>
       <c r="I13" s="4">
-        <f>SUMIF(F13:F116, H13, E13:E116)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="3">
         <v>111</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="3">
         <v>10</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="27"/>
+      <c r="F14" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="G14" s="18"/>
       <c r="H14" s="6"/>
       <c r="I14" s="4">
-        <f>SUMIF(F14:F117, H14, E14:E117)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="3">
         <v>112</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="3">
         <v>8</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="28"/>
+      <c r="F15" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="G15" s="19"/>
       <c r="H15" s="3"/>
       <c r="I15" s="4">
-        <f>SUMIF(F15:F118, H15, E15:E118)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="3">
         <v>112</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="3">
         <v>16</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="24"/>
+      <c r="F16" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="G16" s="14"/>
       <c r="H16" s="3"/>
       <c r="I16" s="4">
-        <f>SUMIF(F16:F119, H16, E16:E119)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="3">
         <v>121</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="28"/>
+      <c r="F17" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="G17" s="19"/>
       <c r="H17" s="3"/>
       <c r="I17" s="4">
-        <f>SUMIF(F17:F120, H17, E17:E120)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="3">
         <v>145</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="28"/>
+      <c r="F18" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="G18" s="19"/>
       <c r="H18" s="3"/>
       <c r="I18" s="4">
-        <f>SUMIF(F18:F121, H18, E18:E121)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="3">
         <v>148</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="3">
         <v>4</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="29"/>
+      <c r="F19" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="G19" s="20"/>
       <c r="H19" s="3"/>
       <c r="I19" s="4">
-        <f>SUMIF(F19:F122, H19, E19:E122)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="3">
         <v>148</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="3">
         <v>9</v>
       </c>
       <c r="F20" s="11"/>
-      <c r="G20" s="29"/>
+      <c r="G20" s="20"/>
       <c r="H20" s="3"/>
       <c r="I20" s="4">
-        <f>SUMIF(F20:F123, H20, E20:E123)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="3">
         <v>150</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="3">
         <v>18</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="29"/>
+      <c r="F21" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G21" s="20"/>
       <c r="H21" s="3"/>
       <c r="I21" s="4">
-        <f>SUMIF(F21:F124, H21, E21:E124)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="3">
         <v>150</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="3">
         <v>10</v>
       </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="29"/>
+      <c r="F22" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G22" s="20"/>
       <c r="H22" s="8"/>
       <c r="I22" s="4">
-        <f>SUMIF(F22:F125, H22, E22:E125)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="3">
         <v>151</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="3">
         <v>30</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="29"/>
+      <c r="F23" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G23" s="20"/>
       <c r="H23" s="3"/>
       <c r="I23" s="4">
-        <f>SUMIF(F23:F126, H23, E23:E126)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="3">
         <v>152</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="3">
         <v>8</v>
       </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="29"/>
+      <c r="F24" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G24" s="20"/>
       <c r="H24" s="3"/>
       <c r="I24" s="4">
-        <f>SUMIF(F24:F127, H24, E24:E127)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="3">
         <v>153</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="3">
         <v>10</v>
       </c>
       <c r="F25" s="11"/>
-      <c r="G25" s="29"/>
+      <c r="G25" s="20"/>
       <c r="H25" s="3"/>
       <c r="I25" s="4">
-        <f>SUMIF(F25:F128, H25, E25:E128)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="3">
         <v>155</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="3">
         <v>10</v>
       </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="29"/>
+      <c r="F26" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G26" s="20"/>
       <c r="H26" s="3"/>
       <c r="I26" s="4">
-        <f>SUMIF(F26:F129, H26, E26:E129)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="3">
         <v>155</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="3">
         <v>7</v>
       </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="30"/>
+      <c r="F27" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="G27" s="21"/>
       <c r="H27" s="3"/>
       <c r="I27" s="4">
-        <f>SUMIF(F27:F130, H27, E27:E130)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="3">
         <v>161</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="3">
         <v>9</v>
       </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="30"/>
+      <c r="F28" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="G28" s="21"/>
       <c r="H28" s="3"/>
       <c r="I28" s="4">
-        <f>SUMIF(F28:F131, H28, E28:E131)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="3">
         <v>161</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="3">
         <v>22</v>
       </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="27"/>
+      <c r="F29" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="G29" s="18"/>
       <c r="H29" s="3"/>
       <c r="I29" s="4">
-        <f>SUMIF(F29:F132, H29, E29:E132)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="3">
         <v>162</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="3">
         <v>8</v>
       </c>
       <c r="F30" s="11"/>
-      <c r="G30" s="24"/>
+      <c r="G30" s="14"/>
       <c r="H30" s="5"/>
       <c r="I30" s="4">
-        <f>SUMIF(F30:F133, H30, E30:E133)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="3">
         <v>163</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="3">
         <v>15</v>
       </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="24"/>
+      <c r="G31" s="14"/>
       <c r="H31" s="3"/>
       <c r="I31" s="4">
-        <f>SUMIF(F31:F134, H31, E31:E134)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="3">
         <v>183</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="3">
         <v>15</v>
       </c>
       <c r="F32" s="11"/>
-      <c r="G32" s="24"/>
+      <c r="G32" s="14"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4">
-        <f>SUMIF(F32:F135, H32, E32:E135)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="3">
         <v>242</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="3">
         <v>13</v>
       </c>
       <c r="F33" s="11"/>
-      <c r="G33" s="24"/>
+      <c r="G33" s="14"/>
       <c r="H33" s="3"/>
       <c r="I33" s="4">
-        <f>SUMIF(F33:F136, H33, E33:E136)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="3">
         <v>243</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="3">
         <v>12</v>
       </c>
       <c r="F34" s="11"/>
-      <c r="G34" s="24"/>
+      <c r="G34" s="14"/>
       <c r="H34" s="3"/>
       <c r="I34" s="4">
-        <f>SUMIF(F34:F137, H34, E34:E137)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="3">
         <v>243</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="3">
         <v>11</v>
       </c>
       <c r="F35" s="11"/>
-      <c r="G35" s="28"/>
+      <c r="G35" s="19"/>
       <c r="H35" s="5"/>
       <c r="I35" s="4">
-        <f>SUMIF(F35:F138, H35, E35:E138)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="3">
         <v>244</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="3">
         <v>14</v>
       </c>
-      <c r="F36" s="17"/>
-      <c r="G36" s="24"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="14"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4">
-        <f>SUMIF(F36:F139, H36, E36:E139)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="3">
         <v>244</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="3">
         <v>13</v>
       </c>
-      <c r="F37" s="17"/>
-      <c r="G37" s="24"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4">
-        <f>SUMIF(F37:F140, H37, E37:E140)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="3">
         <v>254</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="3">
         <v>9</v>
       </c>
       <c r="F38" s="11"/>
-      <c r="G38" s="24"/>
+      <c r="G38" s="14"/>
       <c r="H38" s="3"/>
       <c r="I38" s="4">
-        <f>SUMIF(F38:F141, H38, E38:E141)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="3">
         <v>254</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="3">
         <v>28</v>
       </c>
       <c r="F39" s="11"/>
-      <c r="G39" s="24"/>
+      <c r="G39" s="14"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4">
-        <f>SUMIF(F39:F142, H39, E39:E142)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="3">
         <v>255</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="3">
         <v>3</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="31"/>
+      <c r="F40" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G40" s="22"/>
       <c r="H40" s="5"/>
       <c r="I40" s="4">
-        <f>SUMIF(F40:F143, H40, E40:E143)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="3">
         <v>255</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="3">
         <v>3</v>
       </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="31"/>
+      <c r="F41" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G41" s="22"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4">
-        <f>SUMIF(F41:F144, H41, E41:E144)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="3">
         <v>255</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="3">
         <v>3</v>
       </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="31"/>
+      <c r="F42" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G42" s="22"/>
       <c r="H42" s="3"/>
       <c r="I42" s="4">
-        <f>SUMIF(F42:F145, H42, E42:E145)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="3">
         <v>256</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="3">
         <v>3</v>
       </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="31"/>
+      <c r="F43" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G43" s="22"/>
       <c r="H43" s="5"/>
       <c r="I43" s="4">
-        <f>SUMIF(F43:F146, H43, E43:E146)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="34" t="s">
+      <c r="A44" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="34" t="s">
+      <c r="B44" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="C44" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="25">
         <v>256</v>
       </c>
-      <c r="E44" s="34">
+      <c r="E44" s="25">
         <v>8</v>
       </c>
       <c r="F44" s="11"/>
-      <c r="G44" s="24"/>
+      <c r="G44" s="14"/>
       <c r="I44" s="4">
-        <f>SUMIF(F44:F147, H44, E44:E147)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="3">
         <v>258</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="3">
         <v>19</v>
       </c>
-      <c r="F45" s="18"/>
-      <c r="G45" s="29"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="20"/>
       <c r="I45" s="4">
-        <f>SUMIF(F45:F148, H45, E45:E148)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="3">
         <v>259</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="3">
         <v>30</v>
       </c>
       <c r="F46" s="11"/>
-      <c r="G46" s="31"/>
+      <c r="G46" s="22"/>
       <c r="I46" s="4">
-        <f>SUMIF(F46:F149, H46, E46:E149)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="3">
         <v>263</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="3">
         <v>30</v>
       </c>
-      <c r="F47" s="16"/>
-      <c r="G47" s="24"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="14"/>
       <c r="I47" s="4">
-        <f>SUMIF(F47:F150, H47, E47:E150)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="3">
         <v>265</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="3">
         <v>7</v>
       </c>
-      <c r="F48" s="16"/>
-      <c r="G48" s="31"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="22"/>
       <c r="I48" s="4">
-        <f>SUMIF(F48:F151, H48, E48:E151)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="3">
         <v>266</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="3">
         <v>5</v>
       </c>
-      <c r="F49" s="16"/>
-      <c r="G49" s="24"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="14"/>
       <c r="I49" s="4">
-        <f>SUMIF(F49:F152, H49, E49:E152)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="3">
         <v>266</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="3">
         <v>12</v>
       </c>
       <c r="F50" s="11"/>
-      <c r="G50" s="24"/>
+      <c r="G50" s="14"/>
       <c r="I50" s="4">
-        <f>SUMIF(F50:F153, H50, E50:E153)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="3">
         <v>268</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="3">
         <v>31</v>
       </c>
       <c r="F51" s="11"/>
-      <c r="G51" s="24"/>
+      <c r="G51" s="14"/>
     </row>
     <row r="52" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="3">
         <v>270</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="3">
         <v>16</v>
       </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="31"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="22"/>
     </row>
     <row r="53" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="3">
         <v>272</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="3">
         <v>19</v>
       </c>
-      <c r="F53" s="19"/>
-      <c r="G53" s="24"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
     </row>
     <row r="54" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="3">
         <v>273</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="3">
         <v>16</v>
       </c>
-      <c r="F54" s="19"/>
-      <c r="G54" s="24"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
     </row>
     <row r="55" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="3">
         <v>274</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="3">
         <v>30</v>
       </c>
       <c r="F55" s="11"/>
-      <c r="G55" s="24"/>
+      <c r="G55" s="14"/>
     </row>
     <row r="56" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="3">
         <v>284</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="3">
         <v>12</v>
       </c>
       <c r="F56" s="11"/>
-      <c r="G56" s="24"/>
+      <c r="G56" s="14"/>
     </row>
     <row r="57" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D57" s="3">
         <v>287</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="3">
         <v>41</v>
       </c>
-      <c r="F57" s="11"/>
-      <c r="G57" s="24"/>
+      <c r="F57" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="G57" s="14"/>
     </row>
     <row r="58" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D58" s="16">
+      <c r="D58" s="3">
         <v>291</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="3">
         <v>17</v>
       </c>
-      <c r="F58" s="16"/>
-      <c r="G58" s="31"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="22"/>
     </row>
     <row r="59" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="3">
         <v>292</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="3">
         <v>5</v>
       </c>
-      <c r="F59" s="16"/>
-      <c r="G59" s="31"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="22"/>
     </row>
     <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D60" s="16">
+      <c r="D60" s="3">
         <v>292</v>
       </c>
-      <c r="E60" s="16">
+      <c r="E60" s="3">
         <v>32</v>
       </c>
       <c r="F60" s="11"/>
-      <c r="G60" s="24"/>
+      <c r="G60" s="14"/>
     </row>
     <row r="61" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="3">
         <v>301</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="3">
         <v>42</v>
       </c>
-      <c r="F61" s="11"/>
-      <c r="G61" s="31"/>
+      <c r="F61" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G61" s="22"/>
     </row>
     <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D62" s="16">
+      <c r="D62" s="3">
         <v>304</v>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="3">
         <v>4</v>
       </c>
-      <c r="F62" s="20"/>
-      <c r="G62" s="31"/>
+      <c r="F62" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G62" s="22"/>
     </row>
     <row r="63" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="3">
         <v>305</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="3">
         <v>15</v>
       </c>
-      <c r="F63" s="20"/>
-      <c r="G63" s="28"/>
+      <c r="F63" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G63" s="19"/>
     </row>
     <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D64" s="3">
         <v>313</v>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="3">
         <v>7</v>
       </c>
-      <c r="F64" s="20"/>
-      <c r="G64" s="31"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="22"/>
     </row>
     <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="3">
         <v>313</v>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="3">
         <v>13</v>
       </c>
-      <c r="F65" s="20"/>
-      <c r="G65" s="24"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="14"/>
     </row>
     <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="3">
         <v>314</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="3">
         <v>3</v>
       </c>
-      <c r="F66" s="21"/>
-      <c r="G66" s="31"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="22"/>
     </row>
     <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="3">
         <v>314</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="3">
         <v>12</v>
       </c>
-      <c r="F67" s="21"/>
-      <c r="G67" s="31"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="22"/>
     </row>
     <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C68" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D68" s="16">
+      <c r="D68" s="3">
         <v>315</v>
       </c>
-      <c r="E68" s="16">
+      <c r="E68" s="3">
         <v>12</v>
       </c>
-      <c r="F68" s="12"/>
-      <c r="G68" s="31"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="22"/>
     </row>
     <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D69" s="16">
+      <c r="D69" s="3">
         <v>327</v>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="3">
         <v>20</v>
       </c>
-      <c r="F69" s="16"/>
-      <c r="G69" s="31"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="22"/>
     </row>
     <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C70" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D70" s="16">
+      <c r="D70" s="3">
         <v>329</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="3">
         <v>18</v>
       </c>
-      <c r="F70" s="19"/>
-      <c r="G70" s="24"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
     </row>
     <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="C71" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="3">
         <v>329</v>
       </c>
-      <c r="E71" s="16">
+      <c r="E71" s="3">
         <v>5</v>
       </c>
-      <c r="F71" s="22"/>
-      <c r="G71" s="31"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="22"/>
     </row>
     <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="B72" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C72" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="3">
         <v>329</v>
       </c>
-      <c r="E72" s="16">
+      <c r="E72" s="3">
         <v>17</v>
       </c>
-      <c r="F72" s="14"/>
-      <c r="G72" s="31"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="22"/>
     </row>
     <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="C73" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="3">
         <v>331</v>
       </c>
-      <c r="E73" s="16">
+      <c r="E73" s="3">
         <v>14</v>
       </c>
-      <c r="F73" s="19"/>
-      <c r="G73" s="24"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
     </row>
     <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="B74" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D74" s="16">
+      <c r="D74" s="3">
         <v>331</v>
       </c>
-      <c r="E74" s="16">
+      <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="11"/>
-      <c r="G74" s="24"/>
+      <c r="G74" s="14"/>
     </row>
     <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B75" s="16" t="s">
+      <c r="B75" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="C75" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D75" s="16">
+      <c r="D75" s="3">
         <v>332</v>
       </c>
-      <c r="E75" s="16">
+      <c r="E75" s="3">
         <v>28</v>
       </c>
       <c r="F75" s="11"/>
-      <c r="G75" s="24"/>
+      <c r="G75" s="14"/>
     </row>
     <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D76" s="16">
+      <c r="D76" s="3">
         <v>333</v>
       </c>
-      <c r="E76" s="16">
+      <c r="E76" s="3">
         <v>3</v>
       </c>
-      <c r="F76" s="16"/>
-      <c r="G76" s="31"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="22"/>
     </row>
     <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D77" s="16">
+      <c r="D77" s="3">
         <v>333</v>
       </c>
-      <c r="E77" s="16">
+      <c r="E77" s="3">
         <v>9</v>
       </c>
-      <c r="F77" s="16"/>
-      <c r="G77" s="31"/>
+      <c r="F77" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="G77" s="22"/>
     </row>
     <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B78" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D78" s="16">
+      <c r="D78" s="3">
         <v>334</v>
       </c>
-      <c r="E78" s="16">
+      <c r="E78" s="3">
         <v>13</v>
       </c>
-      <c r="F78" s="21"/>
-      <c r="G78" s="24"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="14"/>
     </row>
     <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C79" s="16" t="s">
+      <c r="C79" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D79" s="16">
+      <c r="D79" s="3">
         <v>336</v>
       </c>
-      <c r="E79" s="16">
+      <c r="E79" s="3">
         <v>15</v>
       </c>
-      <c r="F79" s="21"/>
-      <c r="G79" s="24"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="14"/>
     </row>
     <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D80" s="16">
+      <c r="D80" s="3">
         <v>336</v>
       </c>
-      <c r="E80" s="16">
+      <c r="E80" s="3">
         <v>6</v>
       </c>
-      <c r="F80" s="14"/>
-      <c r="G80" s="31"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="22"/>
     </row>
     <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B81" s="16" t="s">
+      <c r="B81" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C81" s="16" t="s">
+      <c r="C81" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D81" s="16">
+      <c r="D81" s="3">
         <v>337</v>
       </c>
-      <c r="E81" s="16">
+      <c r="E81" s="3">
         <v>4</v>
       </c>
-      <c r="F81" s="14"/>
-      <c r="G81" s="31"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="22"/>
     </row>
     <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B82" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C82" s="16" t="s">
+      <c r="C82" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D82" s="16">
+      <c r="D82" s="3">
         <v>337</v>
       </c>
-      <c r="E82" s="16">
+      <c r="E82" s="3">
         <v>5</v>
       </c>
-      <c r="F82" s="23"/>
-      <c r="G82" s="31"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="22"/>
     </row>
     <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B83" s="16" t="s">
+      <c r="B83" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C83" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D83" s="16">
+      <c r="D83" s="3">
         <v>343</v>
       </c>
-      <c r="E83" s="16">
+      <c r="E83" s="3">
         <v>25</v>
       </c>
-      <c r="F83" s="14"/>
-      <c r="G83" s="31"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="22"/>
     </row>
     <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B84" s="16" t="s">
+      <c r="B84" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D84" s="16">
+      <c r="D84" s="3">
         <v>344</v>
       </c>
-      <c r="E84" s="16">
+      <c r="E84" s="3">
         <v>9</v>
       </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="31"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="22"/>
     </row>
     <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
+      <c r="A85" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B85" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C85" s="16" t="s">
+      <c r="C85" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D85" s="16">
+      <c r="D85" s="3">
         <v>346</v>
       </c>
-      <c r="E85" s="16">
+      <c r="E85" s="3">
         <v>11</v>
       </c>
-      <c r="F85" s="14"/>
-      <c r="G85" s="31"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="22"/>
     </row>
     <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="16" t="s">
+      <c r="A86" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B86" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C86" s="16" t="s">
+      <c r="C86" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D86" s="16">
+      <c r="D86" s="3">
         <v>354</v>
       </c>
-      <c r="E86" s="16">
+      <c r="E86" s="3">
         <v>9</v>
       </c>
       <c r="F86" s="11"/>
-      <c r="G86" s="24"/>
+      <c r="G86" s="14"/>
     </row>
     <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B87" s="16" t="s">
+      <c r="B87" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C87" s="16" t="s">
+      <c r="C87" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D87" s="16">
+      <c r="D87" s="3">
         <v>356</v>
       </c>
-      <c r="E87" s="16">
+      <c r="E87" s="3">
         <v>19</v>
       </c>
       <c r="F87" s="11"/>
-      <c r="G87" s="24"/>
+      <c r="G87" s="14"/>
     </row>
     <row r="88" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="16" t="s">
+      <c r="A88" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B88" s="16" t="s">
+      <c r="B88" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C88" s="16" t="s">
+      <c r="C88" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D88" s="16">
+      <c r="D88" s="3">
         <v>357</v>
       </c>
-      <c r="E88" s="16">
+      <c r="E88" s="3">
         <v>10</v>
       </c>
       <c r="F88" s="11"/>
-      <c r="G88" s="24"/>
+      <c r="G88" s="14"/>
     </row>
     <row r="89" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B89" s="16" t="s">
+      <c r="B89" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C89" s="16" t="s">
+      <c r="C89" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D89" s="16">
+      <c r="D89" s="3">
         <v>357</v>
       </c>
-      <c r="E89" s="16">
+      <c r="E89" s="3">
         <v>13</v>
       </c>
-      <c r="F89" s="16"/>
-      <c r="G89" s="24"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="14"/>
     </row>
     <row r="90" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="16" t="s">
+      <c r="A90" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B90" s="16" t="s">
+      <c r="B90" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C90" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D90" s="16">
+      <c r="D90" s="3">
         <v>360</v>
       </c>
-      <c r="E90" s="16">
+      <c r="E90" s="3">
         <v>16</v>
       </c>
-      <c r="F90" s="14"/>
-      <c r="G90" s="31"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="22"/>
     </row>
     <row r="91" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C91" s="16" t="s">
+      <c r="C91" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D91" s="16">
+      <c r="D91" s="3">
         <v>362</v>
       </c>
-      <c r="E91" s="16">
+      <c r="E91" s="3">
         <v>23</v>
       </c>
-      <c r="F91" s="14"/>
-      <c r="G91" s="31"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="22"/>
     </row>
     <row r="92" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B92" s="16" t="s">
+      <c r="B92" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C92" s="16" t="s">
+      <c r="C92" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D92" s="16">
+      <c r="D92" s="3">
         <v>364</v>
       </c>
-      <c r="E92" s="16">
+      <c r="E92" s="3">
         <v>5</v>
       </c>
-      <c r="F92" s="21"/>
-      <c r="G92" s="31"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="22"/>
     </row>
     <row r="93" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B93" s="16" t="s">
+      <c r="B93" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C93" s="16" t="s">
+      <c r="C93" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D93" s="16">
+      <c r="D93" s="3">
         <v>364</v>
       </c>
-      <c r="E93" s="16">
+      <c r="E93" s="3">
         <v>25</v>
       </c>
-      <c r="F93" s="21"/>
-      <c r="G93" s="31"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="22"/>
     </row>
     <row r="94" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="16" t="s">
+      <c r="A94" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B94" s="16" t="s">
+      <c r="B94" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C94" s="16" t="s">
+      <c r="C94" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D94" s="16">
+      <c r="D94" s="3">
         <v>366</v>
       </c>
-      <c r="E94" s="16">
+      <c r="E94" s="3">
         <v>21</v>
       </c>
-      <c r="F94" s="14"/>
-      <c r="G94" s="31"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="22"/>
     </row>
     <row r="95" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="16" t="s">
+      <c r="A95" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B95" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C95" s="16" t="s">
+      <c r="C95" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="D95" s="16">
+      <c r="D95" s="3">
         <v>367</v>
       </c>
-      <c r="E95" s="16">
+      <c r="E95" s="3">
         <v>16</v>
       </c>
-      <c r="F95" s="23"/>
-      <c r="G95" s="24"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="14"/>
     </row>
     <row r="96" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="16" t="s">
+      <c r="A96" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B96" s="16" t="s">
+      <c r="B96" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C96" s="16" t="s">
+      <c r="C96" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D96" s="16">
+      <c r="D96" s="3">
         <v>368</v>
       </c>
-      <c r="E96" s="16">
+      <c r="E96" s="3">
         <v>9</v>
       </c>
-      <c r="F96" s="16"/>
-      <c r="G96" s="31"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="22"/>
     </row>
     <row r="97" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B97" s="16" t="s">
+      <c r="B97" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C97" s="16" t="s">
+      <c r="C97" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D97" s="16">
+      <c r="D97" s="3">
         <v>367</v>
       </c>
-      <c r="E97" s="16">
+      <c r="E97" s="3">
         <v>5</v>
       </c>
-      <c r="F97" s="14"/>
-      <c r="G97" s="31"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="22"/>
     </row>
     <row r="98" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="16" t="s">
+      <c r="A98" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B98" s="16" t="s">
+      <c r="B98" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C98" s="16" t="s">
+      <c r="C98" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D98" s="16">
+      <c r="D98" s="3">
         <v>367</v>
       </c>
-      <c r="E98" s="16">
+      <c r="E98" s="3">
         <v>14</v>
       </c>
-      <c r="F98" s="16"/>
-      <c r="G98" s="31"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="22"/>
     </row>
     <row r="99" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="B99" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C99" s="16" t="s">
+      <c r="C99" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="D99" s="16">
+      <c r="D99" s="3">
         <v>368</v>
       </c>
-      <c r="E99" s="16">
+      <c r="E99" s="3">
         <v>14</v>
       </c>
-      <c r="F99" s="16"/>
-      <c r="G99" s="31"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="22"/>
     </row>
     <row r="100" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="16" t="s">
+      <c r="A100" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B100" s="16" t="s">
+      <c r="B100" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C100" s="16" t="s">
+      <c r="C100" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D100" s="16">
+      <c r="D100" s="3">
         <v>370</v>
       </c>
-      <c r="E100" s="16">
+      <c r="E100" s="3">
         <v>6</v>
       </c>
-      <c r="F100" s="20"/>
-      <c r="G100" s="24"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="14"/>
     </row>
     <row r="101" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B101" s="16" t="s">
+      <c r="B101" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C101" s="16" t="s">
+      <c r="C101" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D101" s="16">
+      <c r="D101" s="3">
         <v>377</v>
       </c>
-      <c r="E101" s="16">
+      <c r="E101" s="3">
         <v>22</v>
       </c>
       <c r="F101" s="11"/>
-      <c r="G101" s="24"/>
+      <c r="G101" s="14"/>
     </row>
     <row r="102" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B102" s="16" t="s">
+      <c r="B102" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C102" s="16" t="s">
+      <c r="C102" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D102" s="16">
+      <c r="D102" s="3">
         <v>377</v>
       </c>
-      <c r="E102" s="16">
+      <c r="E102" s="3">
         <v>12</v>
       </c>
-      <c r="F102" s="16"/>
-      <c r="G102" s="31"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="22"/>
     </row>
     <row r="103" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B103" s="16" t="s">
+      <c r="B103" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C103" s="16" t="s">
+      <c r="C103" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D103" s="16">
+      <c r="D103" s="3">
         <v>384</v>
       </c>
-      <c r="E103" s="16">
+      <c r="E103" s="3">
         <v>30</v>
       </c>
-      <c r="F103" s="16"/>
-      <c r="G103" s="31"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="22"/>
     </row>
     <row r="104" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B104" s="16" t="s">
+      <c r="B104" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C104" s="16" t="s">
+      <c r="C104" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D104" s="16">
+      <c r="D104" s="3">
         <v>384</v>
       </c>
-      <c r="E104" s="16">
+      <c r="E104" s="3">
         <v>16</v>
       </c>
-      <c r="F104" s="21"/>
-      <c r="G104" s="31"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="22"/>
     </row>
     <row r="105" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B105" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C105" s="16" t="s">
+      <c r="C105" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D105" s="16">
+      <c r="D105" s="3">
         <v>465</v>
       </c>
-      <c r="E105" s="16">
+      <c r="E105" s="3">
         <v>18</v>
       </c>
-      <c r="F105" s="16"/>
-      <c r="G105" s="31"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="22"/>
     </row>
     <row r="106" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="B106" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C106" s="16" t="s">
+      <c r="C106" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D106" s="16">
+      <c r="D106" s="3">
         <v>470</v>
       </c>
-      <c r="E106" s="16">
+      <c r="E106" s="3">
         <v>24</v>
       </c>
-      <c r="F106" s="14"/>
-      <c r="G106" s="31"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="22"/>
     </row>
     <row r="107" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="16" t="s">
+      <c r="A107" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C107" s="16" t="s">
+      <c r="C107" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D107" s="16">
+      <c r="D107" s="3">
         <v>475</v>
       </c>
-      <c r="E107" s="16">
+      <c r="E107" s="3">
         <v>37</v>
       </c>
-      <c r="F107" s="23"/>
-      <c r="G107" s="32"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="23"/>
     </row>
     <row r="108" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D108" s="7" t="s">

--- a/PM/SkienAlgsListPM2025.xlsx
+++ b/PM/SkienAlgsListPM2025.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urfume-my.sharepoint.com/personal/sergey_osipov_urfu_me/Documents/AiSD2026/PM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1297" documentId="13_ncr:1_{BB64072A-02B6-4C3F-B1E2-71C6B558E3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35BC7EB5-76C1-4E73-B4C1-35E98C180939}"/>
+  <xr:revisionPtr revIDLastSave="1301" documentId="13_ncr:1_{BB64072A-02B6-4C3F-B1E2-71C6B558E3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA9C9442-ACDF-476C-A7A3-5E4694D2915B}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="660" windowWidth="24660" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="105" yWindow="750" windowWidth="24660" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="324">
   <si>
     <t>Листинг</t>
   </si>
@@ -1030,6 +1031,9 @@
   </si>
   <si>
     <t>Бельков Сергей Дмитриевич</t>
+  </si>
+  <si>
+    <t>Гультяева Виктория Юрьевна</t>
   </si>
 </sst>
 </file>
@@ -1709,7 +1713,7 @@
       </c>
       <c r="G2" s="14"/>
       <c r="H2" s="3" t="str" cm="1">
-        <f t="array" ref="H2:H9">_xlfn.UNIQUE($F$2:$F$107)</f>
+        <f t="array" ref="H2:H10">_xlfn.UNIQUE($F$2:$F$107)</f>
         <v>Толстобров Дмитрий Александрович</v>
       </c>
       <c r="I2" s="4">
@@ -1870,11 +1874,11 @@
       <c r="F8" s="11"/>
       <c r="G8" s="17"/>
       <c r="H8" s="3" t="str">
-        <v>Бельков Сергей Дмитриевич</v>
+        <v>Гультяева Виктория Юрьевна</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1896,11 +1900,11 @@
       <c r="F9" s="11"/>
       <c r="G9" s="17"/>
       <c r="H9" s="5" t="str">
-        <v>Корнешов Дмитрий Александрович</v>
+        <v>Бельков Сергей Дмитриевич</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1921,10 +1925,12 @@
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="17"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3" t="str">
+        <v>Корнешов Дмитрий Александрович</v>
+      </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2525,7 +2531,9 @@
       <c r="E34" s="3">
         <v>12</v>
       </c>
-      <c r="F34" s="11"/>
+      <c r="F34" s="8" t="s">
+        <v>323</v>
+      </c>
       <c r="G34" s="14"/>
       <c r="H34" s="3"/>
       <c r="I34" s="4">
@@ -2549,7 +2557,9 @@
       <c r="E35" s="3">
         <v>11</v>
       </c>
-      <c r="F35" s="11"/>
+      <c r="F35" s="8" t="s">
+        <v>323</v>
+      </c>
       <c r="G35" s="19"/>
       <c r="H35" s="5"/>
       <c r="I35" s="4">
@@ -2573,7 +2583,9 @@
       <c r="E36" s="3">
         <v>14</v>
       </c>
-      <c r="F36" s="12"/>
+      <c r="F36" s="8" t="s">
+        <v>323</v>
+      </c>
       <c r="G36" s="14"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4">
